--- a/data/outplant/sequim/survival.xlsx
+++ b/data/outplant/sequim/survival.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/polyIC-larvae/data/outplant/sequim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD02F9A2-ABF0-0843-BCA4-6E1EB0B46177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2A2288-A796-3649-8926-567233A5057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="760" windowWidth="14200" windowHeight="16940" xr2:uid="{3D148DFB-94BF-E044-8D7D-CEC1CD506C2E}"/>
+    <workbookView xWindow="14240" yWindow="760" windowWidth="14200" windowHeight="16940" xr2:uid="{3D148DFB-94BF-E044-8D7D-CEC1CD506C2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
   <si>
     <t>outplant_tag</t>
   </si>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B1378F-A6DB-0C46-99D1-FAE05B75BC8B}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -564,6 +564,118 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>20260531</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>20260531</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>20260531</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>20260531</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>20260531</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>20260531</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>20260531</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>20260531</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
